--- a/Datos_de_prueba/01_caso_limpio/PL-02_clases_vida_util.xlsx
+++ b/Datos_de_prueba/01_caso_limpio/PL-02_clases_vida_util.xlsx
@@ -245,7 +245,7 @@
     <t>COM</t>
   </si>
   <si>
-    <t>EQUIPO DE COMUNICACION Y COMPUTACION</t>
+    <t>EQUIPO DE COMUNICACION Y COMPUTO</t>
   </si>
   <si>
     <t>167002</t>
